--- a/output/graficos_dimensiones/comunal_d_env_a_2019_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_antofagasta.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:15</t>
+    <t xml:space="preserve">2026-09-10 01:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_antofagasta.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:29</t>
+    <t xml:space="preserve">2026-09-12 22:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_antofagasta.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:40</t>
+    <t xml:space="preserve">2026-09-24 00:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -502,7 +502,7 @@
         <v>2019</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>73.26</v>
+        <v>78.06</v>
       </c>
     </row>
     <row r="3">
@@ -519,7 +519,7 @@
         <v>2019</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>72.22</v>
+        <v>76.7</v>
       </c>
     </row>
     <row r="4">
@@ -536,7 +536,7 @@
         <v>2019</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>60.79</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="5">
@@ -553,7 +553,7 @@
         <v>2019</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>52.62</v>
+        <v>56.86</v>
       </c>
     </row>
     <row r="6">
@@ -570,7 +570,7 @@
         <v>2019</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>51.8</v>
+        <v>55.08</v>
       </c>
     </row>
     <row r="7">
@@ -587,7 +587,7 @@
         <v>2019</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>49.77</v>
+        <v>52.95</v>
       </c>
     </row>
     <row r="8">
@@ -604,7 +604,7 @@
         <v>2019</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>44</v>
+        <v>45.83</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         <v>2019</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>38.69</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
@@ -638,7 +638,7 @@
         <v>2019</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>30.38</v>
+        <v>32.47</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_antofagasta.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:09</t>
+    <t xml:space="preserve">2026-10-02 16:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_antofagasta.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:07</t>
+    <t xml:space="preserve">2026-10-05 16:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
